--- a/personel_dosyalar/HASAN_İ_/IYT_PLANSIZ_SAHALAR_AKDENIZ.XLSX
+++ b/personel_dosyalar/HASAN_İ_/IYT_PLANSIZ_SAHALAR_AKDENIZ.XLSX
@@ -10,7 +10,7 @@
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sayfa1!$A$1:$P$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sayfa1!$A$1:$Q$127</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="146">
   <si>
     <t>Sıra 
 no</t>
@@ -217,10 +217,6 @@
     <t>ÇALILIK VE SAYLIK</t>
   </si>
   <si>
-    <t>ÖLÇÜ KROKİSİNDE Ç.ALILIK VE SAYLIK
-PAFTASINDA ÇALILIK</t>
-  </si>
-  <si>
     <t>TAPULAMA HARİCİ
 TAŞLIK</t>
   </si>
@@ -231,10 +227,6 @@
     <t>FUNDALIK</t>
   </si>
   <si>
-    <t>TAPULAMA HARİCİ OLDUĞUNDAN YAPILMAYACAK
-5000LİK PAFTASINDAN TAM TESPİT YAPILAMIYOR</t>
-  </si>
-  <si>
     <t>SERA VAR ZEMİNDE ÖLÇÜLECEK Mİ ?</t>
   </si>
   <si>
@@ -270,9 +262,6 @@
     <t>KAYALIK</t>
   </si>
   <si>
-    <t>KANAL KAMULAŞTIRMASINDAN DOLAYI 4E BÖLÜNECEK</t>
-  </si>
-  <si>
     <t>ZEMİNDE DİREK VAR KAMULAŞTIRMA İÇİN ALIM YAPILACAK
 İRTİFAK HAKKINA GÖRE BÖLÜNECEK</t>
   </si>
@@ -280,9 +269,6 @@
     <t>İRTİFAK HAKKINA GÖRE BÖLÜNECEK</t>
   </si>
   <si>
-    <t>İRTİFAK HAKKINA GÖRE SINIRLANDIRILDI.</t>
-  </si>
-  <si>
     <t>11 VE BAĞLARBAŞI 6</t>
   </si>
   <si>
@@ -294,10 +280,6 @@
 EVLER ÖLÇÜLECEK</t>
   </si>
   <si>
-    <t>BAĞLARBAŞI VE KENDİ PAFTASINDA Kİ DERE DURUMUNA GÖRE
-SINIRLANDIRMASI YAPILDI</t>
-  </si>
-  <si>
     <t>DERE</t>
   </si>
   <si>
@@ -406,10 +388,6 @@
   </si>
   <si>
     <t>SAZLIK</t>
-  </si>
-  <si>
-    <t>SEMBOL KONULMUŞ PAFTASINA SAZLIK OLMASI LAZIM
-ÖLÇÜ KROKİSİ VE 22/A EVRAKLARINA BAKILACAK</t>
   </si>
   <si>
     <t>TAŞLIK VE ÇALILIK
@@ -465,6 +443,64 @@
   </si>
   <si>
     <t>YOLA GÖRE 3 E BÖLÜNECEK</t>
+  </si>
+  <si>
+    <t>YAPILDI</t>
+  </si>
+  <si>
+    <t>22/A EVRAKLARINDA BATAKLIK YAZIYOR</t>
+  </si>
+  <si>
+    <t>TESİS EVRAKLARINDA SANIRIM SAZLIK SEMBOLÜ VAR
+22/A EVRAKLARINDA TH  YAZIYOR</t>
+  </si>
+  <si>
+    <t>TESİS EVRAKLARINDA SANIRIM SAZLIK SEMBOLÜ VAR
+22/A EVRAKLARINDA TH  YAZIYOR
+194 ADADAN VERİLECEK</t>
+  </si>
+  <si>
+    <t>TAPULAMA HARİCİ ORMAN OLDUĞUNDAN YAPILMAYACAK
+5000LİK PAFTASINDAN TAM TESPİT YAPILAMIYOR</t>
+  </si>
+  <si>
+    <t>TAPULAMA HARİCİ ORMAN OLDUĞUNDAN YAPILMAYACAK</t>
+  </si>
+  <si>
+    <t>2B DEĞİYOR G8 OLACAK
+DAVALI 2022/265 3.ASLİYE HUKUK</t>
+  </si>
+  <si>
+    <t>ÖLÇÜ KROKİSİNDE Ç.ALILIK VE SAYLIK
+PAFTASINDA ÇALILIK
+161 ADA</t>
+  </si>
+  <si>
+    <t>161 ADA</t>
+  </si>
+  <si>
+    <t>İRTİFAK HAKKINA GÖRE SINIRLANDIRILDI.
+TAMAMINDA SİT ALANI VARDIR</t>
+  </si>
+  <si>
+    <t>İRTİFAK HAKKINA GÖRE BÖLÜNECEK
+SİT ALANINA GÖRE BÖLÜNECEK</t>
+  </si>
+  <si>
+    <t>KANAL KAMULAŞTIRMASINDAN DOLAYI 4E BÖLÜNECEK
+SİT ALANINA GÖRE BÖLÜNECEK</t>
+  </si>
+  <si>
+    <t>BAĞLARBAŞI VE KENDİ PAFTASINDA Kİ DERE DURUMUNA GÖRE
+SINIRLANDIRMASI YAPILDI
+SİT ALANINA GÖRE BÖLÜNECEK</t>
+  </si>
+  <si>
+    <t>Bölüm
+Sayısı</t>
+  </si>
+  <si>
+    <t>TOPLAM</t>
   </si>
 </sst>
 </file>
@@ -555,7 +591,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -638,13 +674,25 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -928,7 +976,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:P128"/>
+  <dimension ref="A1:Q129"/>
   <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="9"/>
@@ -944,11 +992,12 @@
     <col min="11" max="11" width="23.140625" style="9" customWidth="1"/>
     <col min="12" max="12" width="17.42578125" style="9" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.5703125" style="9" customWidth="1"/>
-    <col min="14" max="14" width="74.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="9"/>
+    <col min="14" max="14" width="13.5703125" style="7" customWidth="1"/>
+    <col min="15" max="15" width="74.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="4" customFormat="1" ht="84" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="4" customFormat="1" ht="84" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -989,12 +1038,15 @@
         <v>10</v>
       </c>
       <c r="N1" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="O1" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="3"/>
       <c r="P1" s="3"/>
-    </row>
-    <row r="2" spans="1:16" s="7" customFormat="1" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q1" s="3"/>
+    </row>
+    <row r="2" spans="1:17" s="7" customFormat="1" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1017,10 +1069,10 @@
         <v>6</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>16</v>
+        <v>113</v>
+      </c>
+      <c r="I2" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>16</v>
@@ -1029,14 +1081,17 @@
         <v>37</v>
       </c>
       <c r="L2" s="5"/>
-      <c r="M2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" s="7" customFormat="1" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M2" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" s="5">
+        <v>1</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" s="7" customFormat="1" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1059,10 +1114,10 @@
         <v>6</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>16</v>
+        <v>113</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J3" s="5" t="s">
         <v>16</v>
@@ -1071,14 +1126,17 @@
         <v>37</v>
       </c>
       <c r="L3" s="5"/>
-      <c r="M3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" s="7" customFormat="1" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M3" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" s="5">
+        <v>1</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" s="7" customFormat="1" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1101,10 +1159,10 @@
         <v>6</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>16</v>
+        <v>113</v>
+      </c>
+      <c r="I4" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J4" s="5" t="s">
         <v>16</v>
@@ -1113,18 +1171,21 @@
         <v>37</v>
       </c>
       <c r="L4" s="5"/>
-      <c r="M4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" s="7" customFormat="1" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M4" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" s="7" customFormat="1" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="29">
         <v>67971</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -1133,40 +1194,41 @@
       <c r="D5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="5">
-        <v>3</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="L5" s="6"/>
-      <c r="M5" s="5" t="s">
+      <c r="F5" s="23">
+        <v>3</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5" s="24"/>
+      <c r="M5" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N5" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N5" s="23"/>
+      <c r="O5" s="24" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="29">
         <v>109838</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -1175,40 +1237,41 @@
       <c r="D6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="5">
-        <v>3</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5" t="s">
+      <c r="F6" s="23">
+        <v>3</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N6" s="6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N6" s="23"/>
+      <c r="O6" s="24" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="29">
         <v>72853</v>
       </c>
       <c r="C7" s="8" t="s">
@@ -1217,40 +1280,41 @@
       <c r="D7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="5">
-        <v>3</v>
-      </c>
-      <c r="G7" s="5">
-        <v>15</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5" t="s">
+      <c r="F7" s="23">
+        <v>3</v>
+      </c>
+      <c r="G7" s="23">
+        <v>15</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="J7" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N7" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N7" s="23"/>
+      <c r="O7" s="23" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="29">
         <v>72865</v>
       </c>
       <c r="C8" s="8" t="s">
@@ -1259,36 +1323,37 @@
       <c r="D8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="5">
-        <v>3</v>
-      </c>
-      <c r="G8" s="5">
-        <v>15</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5" t="s">
+      <c r="F8" s="23">
+        <v>3</v>
+      </c>
+      <c r="G8" s="23">
+        <v>15</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L8" s="23"/>
+      <c r="M8" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N8" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N8" s="23"/>
+      <c r="O8" s="23" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -1313,8 +1378,8 @@
       <c r="H9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>16</v>
+      <c r="I9" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>16</v>
@@ -1323,16 +1388,19 @@
         <v>37</v>
       </c>
       <c r="L9" s="5"/>
-      <c r="M9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N9" s="5"/>
-    </row>
-    <row r="10" spans="1:16" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M9" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N9" s="5">
+        <v>1</v>
+      </c>
+      <c r="O9" s="5"/>
+    </row>
+    <row r="10" spans="1:17" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="29">
         <v>72949</v>
       </c>
       <c r="C10" s="8" t="s">
@@ -1341,36 +1409,37 @@
       <c r="D10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="5">
-        <v>3</v>
-      </c>
-      <c r="G10" s="5">
+      <c r="F10" s="23">
+        <v>3</v>
+      </c>
+      <c r="G10" s="23">
         <v>10</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="J10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5" t="s">
+      <c r="J10" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K10" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L10" s="23"/>
+      <c r="M10" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N10" s="6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N10" s="23"/>
+      <c r="O10" s="24" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -1395,8 +1464,8 @@
       <c r="H11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="6" t="s">
-        <v>16</v>
+      <c r="I11" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>13</v>
@@ -1408,11 +1477,14 @@
       <c r="M11" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="N11" s="5" t="s">
+      <c r="N11" s="5">
+        <v>1</v>
+      </c>
+      <c r="O11" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -1437,8 +1509,8 @@
       <c r="H12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="I12" s="6" t="s">
-        <v>16</v>
+      <c r="I12" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>13</v>
@@ -1450,9 +1522,12 @@
       <c r="M12" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:16" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N12" s="5">
+        <v>1</v>
+      </c>
+      <c r="O12" s="6"/>
+    </row>
+    <row r="13" spans="1:17" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -1477,8 +1552,8 @@
       <c r="H13" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>16</v>
+      <c r="I13" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>13</v>
@@ -1490,9 +1565,12 @@
       <c r="M13" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:16" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N13" s="5">
+        <v>1</v>
+      </c>
+      <c r="O13" s="6"/>
+    </row>
+    <row r="14" spans="1:17" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -1517,8 +1595,8 @@
       <c r="H14" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>16</v>
+      <c r="I14" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>13</v>
@@ -1530,11 +1608,14 @@
       <c r="M14" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="N14" s="6" t="s">
+      <c r="N14" s="5">
+        <v>1</v>
+      </c>
+      <c r="O14" s="6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -1554,13 +1635,13 @@
         <v>3</v>
       </c>
       <c r="G15" s="16">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I15" s="6" t="s">
-        <v>16</v>
+      <c r="I15" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>13</v>
@@ -1572,11 +1653,14 @@
       <c r="M15" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="N15" s="5" t="s">
+      <c r="N15" s="5">
+        <v>1</v>
+      </c>
+      <c r="O15" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -1601,8 +1685,8 @@
       <c r="H16" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I16" s="6" t="s">
-        <v>16</v>
+      <c r="I16" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>13</v>
@@ -1614,9 +1698,12 @@
       <c r="M16" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="N16" s="5"/>
-    </row>
-    <row r="17" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N16" s="5">
+        <v>1</v>
+      </c>
+      <c r="O16" s="5"/>
+    </row>
+    <row r="17" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -1641,8 +1728,8 @@
       <c r="H17" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I17" s="6" t="s">
-        <v>16</v>
+      <c r="I17" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>37</v>
@@ -1654,11 +1741,14 @@
       <c r="M17" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="N17" s="6" t="s">
+      <c r="N17" s="5">
+        <v>1</v>
+      </c>
+      <c r="O17" s="6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -1683,8 +1773,8 @@
       <c r="H18" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I18" s="6" t="s">
-        <v>16</v>
+      <c r="I18" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>13</v>
@@ -1696,15 +1786,18 @@
       <c r="M18" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="N18" s="6" t="s">
+      <c r="N18" s="5">
+        <v>1</v>
+      </c>
+      <c r="O18" s="6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>18</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="29">
         <v>109495</v>
       </c>
       <c r="C19" s="8" t="s">
@@ -1713,36 +1806,37 @@
       <c r="D19" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="E19" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="F19" s="5">
-        <v>3</v>
-      </c>
-      <c r="G19" s="5">
+      <c r="F19" s="23">
+        <v>3</v>
+      </c>
+      <c r="G19" s="23">
         <v>2</v>
       </c>
       <c r="H19" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="I19" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L19" s="5"/>
+      <c r="I19" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="K19" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L19" s="23"/>
       <c r="M19" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N19" s="23" t="s">
+      <c r="N19" s="23"/>
+      <c r="O19" s="23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -1767,8 +1861,8 @@
       <c r="H20" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="I20" s="6" t="s">
-        <v>16</v>
+      <c r="I20" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>15</v>
@@ -1780,11 +1874,14 @@
       <c r="M20" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="N20" s="6" t="s">
+      <c r="N20" s="5">
+        <v>1</v>
+      </c>
+      <c r="O20" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -1807,10 +1904,10 @@
         <v>3</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>16</v>
+        <v>114</v>
+      </c>
+      <c r="I21" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>13</v>
@@ -1819,16 +1916,19 @@
         <v>13</v>
       </c>
       <c r="L21" s="5"/>
-      <c r="M21" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N21" s="5"/>
-    </row>
-    <row r="22" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M21" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N21" s="5">
+        <v>1</v>
+      </c>
+      <c r="O21" s="5"/>
+    </row>
+    <row r="22" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>21</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="29">
         <v>35298</v>
       </c>
       <c r="C22" s="8" t="s">
@@ -1837,40 +1937,41 @@
       <c r="D22" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="F22" s="5">
-        <v>3</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5" t="s">
+      <c r="F22" s="23">
+        <v>3</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="H22" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="I22" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="J22" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="K22" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="L22" s="23"/>
+      <c r="M22" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N22" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N22" s="23"/>
+      <c r="O22" s="23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>22</v>
       </c>
-      <c r="B23" s="19">
+      <c r="B23" s="29">
         <v>142484</v>
       </c>
       <c r="C23" s="8" t="s">
@@ -1879,40 +1980,41 @@
       <c r="D23" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="22" t="s">
+      <c r="E23" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="F23" s="5">
-        <v>3</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5" t="s">
+      <c r="F23" s="23">
+        <v>3</v>
+      </c>
+      <c r="G23" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="H23" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="I23" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="J23" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="K23" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N23" s="5" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N23" s="23"/>
+      <c r="O23" s="23" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>23</v>
       </c>
-      <c r="B24" s="19">
+      <c r="B24" s="29">
         <v>30152</v>
       </c>
       <c r="C24" s="8" t="s">
@@ -1921,40 +2023,41 @@
       <c r="D24" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E24" s="22" t="s">
+      <c r="E24" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F24" s="5">
-        <v>3</v>
-      </c>
-      <c r="G24" s="5">
+      <c r="F24" s="23">
+        <v>3</v>
+      </c>
+      <c r="G24" s="23">
         <v>4</v>
       </c>
       <c r="H24" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="I24" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L24" s="5"/>
+      <c r="I24" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J24" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K24" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L24" s="23"/>
       <c r="M24" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N24" s="24" t="s">
+      <c r="N24" s="23"/>
+      <c r="O24" s="24" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>24</v>
       </c>
-      <c r="B25" s="19">
+      <c r="B25" s="29">
         <v>30158</v>
       </c>
       <c r="C25" s="8" t="s">
@@ -1963,40 +2066,41 @@
       <c r="D25" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="22" t="s">
+      <c r="E25" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F25" s="5">
-        <v>3</v>
-      </c>
-      <c r="G25" s="5">
+      <c r="F25" s="23">
+        <v>3</v>
+      </c>
+      <c r="G25" s="23">
         <v>3</v>
       </c>
       <c r="H25" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="I25" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L25" s="5"/>
+      <c r="I25" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J25" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K25" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L25" s="23"/>
       <c r="M25" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N25" s="24" t="s">
+      <c r="N25" s="23"/>
+      <c r="O25" s="24" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>25</v>
       </c>
-      <c r="B26" s="19">
+      <c r="B26" s="29">
         <v>30831</v>
       </c>
       <c r="C26" s="8" t="s">
@@ -2005,36 +2109,37 @@
       <c r="D26" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="22" t="s">
+      <c r="E26" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F26" s="5">
-        <v>3</v>
-      </c>
-      <c r="G26" s="5">
+      <c r="F26" s="23">
+        <v>3</v>
+      </c>
+      <c r="G26" s="23">
         <v>4</v>
       </c>
       <c r="H26" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="I26" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L26" s="5"/>
+      <c r="I26" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J26" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K26" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L26" s="23"/>
       <c r="M26" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N26" s="24" t="s">
+      <c r="N26" s="23"/>
+      <c r="O26" s="24" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -2059,8 +2164,8 @@
       <c r="H27" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I27" s="5" t="s">
-        <v>16</v>
+      <c r="I27" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>16</v>
@@ -2072,9 +2177,12 @@
       <c r="M27" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="N27" s="6"/>
-    </row>
-    <row r="28" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N27" s="5">
+        <v>1</v>
+      </c>
+      <c r="O27" s="6"/>
+    </row>
+    <row r="28" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -2099,8 +2207,8 @@
       <c r="H28" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="I28" s="5" t="s">
-        <v>16</v>
+      <c r="I28" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>16</v>
@@ -2112,11 +2220,14 @@
       <c r="M28" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="N28" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N28" s="5">
+        <v>1</v>
+      </c>
+      <c r="O28" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -2141,8 +2252,8 @@
       <c r="H29" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I29" s="5" t="s">
-        <v>16</v>
+      <c r="I29" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>16</v>
@@ -2154,13 +2265,18 @@
       <c r="M29" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="N29" s="5"/>
-    </row>
-    <row r="30" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N29" s="5">
+        <v>1</v>
+      </c>
+      <c r="O29" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>29</v>
       </c>
-      <c r="B30" s="19">
+      <c r="B30" s="29">
         <v>31852</v>
       </c>
       <c r="C30" s="8" t="s">
@@ -2169,40 +2285,41 @@
       <c r="D30" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E30" s="22" t="s">
+      <c r="E30" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F30" s="5">
-        <v>3</v>
-      </c>
-      <c r="G30" s="5">
+      <c r="F30" s="23">
+        <v>3</v>
+      </c>
+      <c r="G30" s="23">
         <v>4</v>
       </c>
       <c r="H30" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="I30" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L30" s="5"/>
+      <c r="I30" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J30" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K30" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L30" s="23"/>
       <c r="M30" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N30" s="24" t="s">
+      <c r="N30" s="23"/>
+      <c r="O30" s="24" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>30</v>
       </c>
-      <c r="B31" s="19">
+      <c r="B31" s="29">
         <v>31868</v>
       </c>
       <c r="C31" s="8" t="s">
@@ -2211,40 +2328,41 @@
       <c r="D31" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="22" t="s">
+      <c r="E31" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F31" s="5">
-        <v>3</v>
-      </c>
-      <c r="G31" s="5">
+      <c r="F31" s="23">
+        <v>3</v>
+      </c>
+      <c r="G31" s="23">
         <v>6</v>
       </c>
       <c r="H31" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="I31" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L31" s="5"/>
+      <c r="I31" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K31" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L31" s="23"/>
       <c r="M31" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N31" s="24" t="s">
+      <c r="N31" s="23"/>
+      <c r="O31" s="24" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>31</v>
       </c>
-      <c r="B32" s="19">
+      <c r="B32" s="29">
         <v>31870</v>
       </c>
       <c r="C32" s="8" t="s">
@@ -2253,36 +2371,37 @@
       <c r="D32" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E32" s="22" t="s">
+      <c r="E32" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F32" s="5">
-        <v>3</v>
-      </c>
-      <c r="G32" s="5">
+      <c r="F32" s="23">
+        <v>3</v>
+      </c>
+      <c r="G32" s="23">
         <v>6</v>
       </c>
       <c r="H32" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="I32" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J32" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L32" s="5"/>
+      <c r="I32" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J32" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K32" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L32" s="23"/>
       <c r="M32" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N32" s="24" t="s">
+      <c r="N32" s="23"/>
+      <c r="O32" s="24" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -2307,8 +2426,8 @@
       <c r="H33" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I33" s="8" t="s">
-        <v>37</v>
+      <c r="I33" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J33" s="8" t="s">
         <v>37</v>
@@ -2320,13 +2439,16 @@
       <c r="M33" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="N33" s="8"/>
-    </row>
-    <row r="34" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N33" s="5">
+        <v>1</v>
+      </c>
+      <c r="O33" s="8"/>
+    </row>
+    <row r="34" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>33</v>
       </c>
-      <c r="B34" s="19">
+      <c r="B34" s="29">
         <v>31883</v>
       </c>
       <c r="C34" s="8" t="s">
@@ -2335,36 +2457,37 @@
       <c r="D34" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E34" s="22" t="s">
+      <c r="E34" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F34" s="5">
-        <v>3</v>
-      </c>
-      <c r="G34" s="5">
+      <c r="F34" s="23">
+        <v>3</v>
+      </c>
+      <c r="G34" s="23">
         <v>7</v>
       </c>
       <c r="H34" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="I34" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J34" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K34" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L34" s="5"/>
+      <c r="I34" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J34" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K34" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L34" s="23"/>
       <c r="M34" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N34" s="24" t="s">
+      <c r="N34" s="23"/>
+      <c r="O34" s="24" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -2389,8 +2512,8 @@
       <c r="H35" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I35" s="5" t="s">
-        <v>13</v>
+      <c r="I35" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J35" s="5" t="s">
         <v>16</v>
@@ -2402,15 +2525,18 @@
       <c r="M35" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="N35" s="6" t="s">
+      <c r="N35" s="5">
+        <v>1</v>
+      </c>
+      <c r="O35" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>35</v>
       </c>
-      <c r="B36" s="19">
+      <c r="B36" s="29">
         <v>31907</v>
       </c>
       <c r="C36" s="8" t="s">
@@ -2419,40 +2545,41 @@
       <c r="D36" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E36" s="22" t="s">
+      <c r="E36" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F36" s="5">
-        <v>3</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>61</v>
+      <c r="F36" s="23">
+        <v>3</v>
+      </c>
+      <c r="G36" s="23" t="s">
+        <v>60</v>
       </c>
       <c r="H36" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="I36" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J36" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K36" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L36" s="5"/>
+      <c r="I36" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J36" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K36" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L36" s="23"/>
       <c r="M36" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N36" s="24" t="s">
+      <c r="N36" s="23"/>
+      <c r="O36" s="24" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>36</v>
       </c>
-      <c r="B37" s="19">
+      <c r="B37" s="29">
         <v>31922</v>
       </c>
       <c r="C37" s="8" t="s">
@@ -2461,40 +2588,41 @@
       <c r="D37" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E37" s="22" t="s">
+      <c r="E37" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F37" s="5">
-        <v>3</v>
-      </c>
-      <c r="G37" s="5" t="s">
+      <c r="F37" s="23">
+        <v>3</v>
+      </c>
+      <c r="G37" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="H37" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I37" s="5" t="s">
+      <c r="H37" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="I37" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="J37" s="5" t="s">
+      <c r="J37" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="K37" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="L37" s="5"/>
-      <c r="M37" s="25" t="s">
+      <c r="K37" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="L37" s="23"/>
+      <c r="M37" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N37" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N37" s="23"/>
+      <c r="O37" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>37</v>
       </c>
-      <c r="B38" s="19">
+      <c r="B38" s="29">
         <v>31983</v>
       </c>
       <c r="C38" s="8" t="s">
@@ -2503,40 +2631,41 @@
       <c r="D38" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E38" s="22" t="s">
+      <c r="E38" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F38" s="5">
-        <v>3</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>65</v>
+      <c r="F38" s="23">
+        <v>3</v>
+      </c>
+      <c r="G38" s="24" t="s">
+        <v>63</v>
       </c>
       <c r="H38" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="I38" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J38" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K38" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L38" s="5"/>
+        <v>64</v>
+      </c>
+      <c r="I38" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K38" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L38" s="23"/>
       <c r="M38" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N38" s="24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N38" s="23"/>
+      <c r="O38" s="24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>38</v>
       </c>
-      <c r="B39" s="19">
+      <c r="B39" s="29">
         <v>31991</v>
       </c>
       <c r="C39" s="8" t="s">
@@ -2545,36 +2674,37 @@
       <c r="D39" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E39" s="22" t="s">
+      <c r="E39" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F39" s="5">
-        <v>3</v>
-      </c>
-      <c r="G39" s="5">
+      <c r="F39" s="23">
+        <v>3</v>
+      </c>
+      <c r="G39" s="23">
         <v>4</v>
       </c>
       <c r="H39" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="I39" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J39" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K39" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L39" s="5"/>
+      <c r="I39" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J39" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K39" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L39" s="23"/>
       <c r="M39" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N39" s="24" t="s">
+      <c r="N39" s="23"/>
+      <c r="O39" s="24" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>39</v>
       </c>
@@ -2594,13 +2724,13 @@
         <v>3</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I40" s="6" t="s">
-        <v>16</v>
+      <c r="I40" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J40" s="5" t="s">
         <v>16</v>
@@ -2612,15 +2742,18 @@
       <c r="M40" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="N40" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N40" s="5">
+        <v>1</v>
+      </c>
+      <c r="O40" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>40</v>
       </c>
-      <c r="B41" s="19">
+      <c r="B41" s="29">
         <v>32054</v>
       </c>
       <c r="C41" s="8" t="s">
@@ -2629,40 +2762,41 @@
       <c r="D41" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E41" s="22" t="s">
+      <c r="E41" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F41" s="5">
-        <v>3</v>
-      </c>
-      <c r="G41" s="5" t="s">
+      <c r="F41" s="23">
+        <v>3</v>
+      </c>
+      <c r="G41" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="H41" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="H41" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I41" s="6" t="s">
+      <c r="I41" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="J41" s="5" t="s">
+      <c r="J41" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="K41" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L41" s="5"/>
-      <c r="M41" s="25" t="s">
+      <c r="K41" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L41" s="23"/>
+      <c r="M41" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N41" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N41" s="23"/>
+      <c r="O41" s="24" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>41</v>
       </c>
-      <c r="B42" s="19">
+      <c r="B42" s="29">
         <v>32074</v>
       </c>
       <c r="C42" s="8" t="s">
@@ -2671,40 +2805,41 @@
       <c r="D42" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E42" s="22" t="s">
+      <c r="E42" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F42" s="5">
-        <v>3</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>61</v>
+      <c r="F42" s="23">
+        <v>3</v>
+      </c>
+      <c r="G42" s="23" t="s">
+        <v>60</v>
       </c>
       <c r="H42" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="I42" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J42" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K42" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L42" s="5"/>
+      <c r="I42" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J42" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K42" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L42" s="23"/>
       <c r="M42" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N42" s="24" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N42" s="23"/>
+      <c r="O42" s="24" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>42</v>
       </c>
-      <c r="B43" s="19">
+      <c r="B43" s="29">
         <v>32079</v>
       </c>
       <c r="C43" s="8" t="s">
@@ -2713,40 +2848,41 @@
       <c r="D43" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E43" s="22" t="s">
+      <c r="E43" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F43" s="5">
-        <v>3</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>61</v>
+      <c r="F43" s="23">
+        <v>3</v>
+      </c>
+      <c r="G43" s="23" t="s">
+        <v>60</v>
       </c>
       <c r="H43" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="I43" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J43" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K43" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L43" s="5"/>
+      <c r="I43" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J43" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K43" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L43" s="23"/>
       <c r="M43" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N43" s="24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N43" s="23"/>
+      <c r="O43" s="24" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>43</v>
       </c>
-      <c r="B44" s="19">
+      <c r="B44" s="29">
         <v>32088</v>
       </c>
       <c r="C44" s="8" t="s">
@@ -2755,40 +2891,41 @@
       <c r="D44" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E44" s="22" t="s">
+      <c r="E44" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F44" s="5">
-        <v>3</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>61</v>
+      <c r="F44" s="23">
+        <v>3</v>
+      </c>
+      <c r="G44" s="23" t="s">
+        <v>60</v>
       </c>
       <c r="H44" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="I44" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J44" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K44" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L44" s="5"/>
+      <c r="I44" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J44" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K44" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L44" s="23"/>
       <c r="M44" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N44" s="24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" s="7" customFormat="1" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N44" s="23"/>
+      <c r="O44" s="24" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" s="7" customFormat="1" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>44</v>
       </c>
-      <c r="B45" s="19">
+      <c r="B45" s="29">
         <v>32091</v>
       </c>
       <c r="C45" s="8" t="s">
@@ -2797,40 +2934,41 @@
       <c r="D45" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E45" s="22" t="s">
+      <c r="E45" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F45" s="5">
-        <v>3</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>61</v>
+      <c r="F45" s="23">
+        <v>3</v>
+      </c>
+      <c r="G45" s="23" t="s">
+        <v>60</v>
       </c>
       <c r="H45" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="I45" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J45" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K45" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L45" s="5"/>
+      <c r="I45" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K45" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L45" s="23"/>
       <c r="M45" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N45" s="24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" s="7" customFormat="1" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N45" s="23"/>
+      <c r="O45" s="24" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" s="7" customFormat="1" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>45</v>
       </c>
-      <c r="B46" s="19">
+      <c r="B46" s="29">
         <v>191736</v>
       </c>
       <c r="C46" s="8" t="s">
@@ -2839,40 +2977,41 @@
       <c r="D46" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E46" s="22" t="s">
+      <c r="E46" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F46" s="5">
-        <v>3</v>
-      </c>
-      <c r="G46" s="5">
+      <c r="F46" s="23">
+        <v>3</v>
+      </c>
+      <c r="G46" s="23">
         <v>4</v>
       </c>
       <c r="H46" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="I46" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J46" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K46" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L46" s="5"/>
+      <c r="I46" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J46" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K46" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L46" s="23"/>
       <c r="M46" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N46" s="24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" s="7" customFormat="1" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N46" s="23"/>
+      <c r="O46" s="24" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" s="7" customFormat="1" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>46</v>
       </c>
-      <c r="B47" s="19">
+      <c r="B47" s="29">
         <v>191741</v>
       </c>
       <c r="C47" s="8" t="s">
@@ -2881,40 +3020,41 @@
       <c r="D47" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E47" s="22" t="s">
+      <c r="E47" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F47" s="5">
-        <v>3</v>
-      </c>
-      <c r="G47" s="5">
+      <c r="F47" s="23">
+        <v>3</v>
+      </c>
+      <c r="G47" s="23">
         <v>4</v>
       </c>
       <c r="H47" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="I47" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J47" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K47" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L47" s="5"/>
+      <c r="I47" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J47" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K47" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L47" s="23"/>
       <c r="M47" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N47" s="24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N47" s="23"/>
+      <c r="O47" s="24" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>47</v>
       </c>
-      <c r="B48" s="19">
+      <c r="B48" s="29">
         <v>109617</v>
       </c>
       <c r="C48" s="8" t="s">
@@ -2923,40 +3063,41 @@
       <c r="D48" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E48" s="22" t="s">
+      <c r="E48" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="F48" s="5">
-        <v>3</v>
-      </c>
-      <c r="G48" s="5">
+      <c r="F48" s="23">
+        <v>3</v>
+      </c>
+      <c r="G48" s="23">
         <v>9</v>
       </c>
-      <c r="H48" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="I48" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="J48" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="K48" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L48" s="5"/>
-      <c r="M48" s="5" t="s">
+      <c r="H48" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="I48" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="J48" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="K48" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L48" s="23"/>
+      <c r="M48" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N48" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N48" s="23"/>
+      <c r="O48" s="24" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>48</v>
       </c>
-      <c r="B49" s="19">
+      <c r="B49" s="29">
         <v>109651</v>
       </c>
       <c r="C49" s="8" t="s">
@@ -2965,36 +3106,37 @@
       <c r="D49" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E49" s="22" t="s">
+      <c r="E49" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="F49" s="5">
-        <v>3</v>
-      </c>
-      <c r="G49" s="5">
+      <c r="F49" s="23">
+        <v>3</v>
+      </c>
+      <c r="G49" s="23">
         <v>8</v>
       </c>
-      <c r="H49" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="I49" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J49" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K49" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L49" s="5"/>
-      <c r="M49" s="5" t="s">
+      <c r="H49" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="I49" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J49" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K49" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L49" s="23"/>
+      <c r="M49" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N49" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N49" s="23"/>
+      <c r="O49" s="24" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>49</v>
       </c>
@@ -3019,8 +3161,8 @@
       <c r="H50" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="I50" s="5" t="s">
-        <v>16</v>
+      <c r="I50" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J50" s="5" t="s">
         <v>36</v>
@@ -3032,11 +3174,14 @@
       <c r="M50" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="N50" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N50" s="5">
+        <v>1</v>
+      </c>
+      <c r="O50" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -3061,8 +3206,8 @@
       <c r="H51" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="I51" s="5" t="s">
-        <v>16</v>
+      <c r="I51" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J51" s="5" t="s">
         <v>36</v>
@@ -3074,11 +3219,14 @@
       <c r="M51" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="N51" s="6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N51" s="5">
+        <v>3</v>
+      </c>
+      <c r="O51" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -3103,8 +3251,8 @@
       <c r="H52" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I52" s="5" t="s">
-        <v>16</v>
+      <c r="I52" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J52" s="5" t="s">
         <v>13</v>
@@ -3113,12 +3261,15 @@
         <v>13</v>
       </c>
       <c r="L52" s="5"/>
-      <c r="M52" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N52" s="6"/>
-    </row>
-    <row r="53" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M52" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N52" s="5">
+        <v>1</v>
+      </c>
+      <c r="O52" s="6"/>
+    </row>
+    <row r="53" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>52</v>
       </c>
@@ -3138,13 +3289,13 @@
         <v>3</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I53" s="5" t="s">
-        <v>16</v>
+      <c r="I53" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J53" s="5" t="s">
         <v>37</v>
@@ -3153,14 +3304,17 @@
         <v>37</v>
       </c>
       <c r="L53" s="5"/>
-      <c r="M53" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N53" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M53" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N53" s="5">
+        <v>1</v>
+      </c>
+      <c r="O53" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>53</v>
       </c>
@@ -3185,8 +3339,8 @@
       <c r="H54" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I54" s="6" t="s">
-        <v>16</v>
+      <c r="I54" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J54" s="5" t="s">
         <v>13</v>
@@ -3195,12 +3349,15 @@
         <v>13</v>
       </c>
       <c r="L54" s="5"/>
-      <c r="M54" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N54" s="6"/>
-    </row>
-    <row r="55" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M54" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N54" s="5">
+        <v>1</v>
+      </c>
+      <c r="O54" s="6"/>
+    </row>
+    <row r="55" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>54</v>
       </c>
@@ -3220,13 +3377,13 @@
         <v>3</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I55" s="6" t="s">
-        <v>16</v>
+      <c r="I55" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J55" s="5" t="s">
         <v>13</v>
@@ -3235,18 +3392,21 @@
         <v>13</v>
       </c>
       <c r="L55" s="5"/>
-      <c r="M55" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N55" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M55" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N55" s="5">
+        <v>2</v>
+      </c>
+      <c r="O55" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>55</v>
       </c>
-      <c r="B56" s="19">
+      <c r="B56" s="29">
         <v>34740</v>
       </c>
       <c r="C56" s="8" t="s">
@@ -3255,36 +3415,37 @@
       <c r="D56" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E56" s="22" t="s">
+      <c r="E56" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="F56" s="5">
-        <v>3</v>
-      </c>
-      <c r="G56" s="16">
+      <c r="F56" s="23">
+        <v>3</v>
+      </c>
+      <c r="G56" s="31">
         <v>6</v>
       </c>
-      <c r="H56" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="I56" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="J56" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K56" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L56" s="5"/>
-      <c r="M56" s="5" t="s">
+      <c r="H56" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="I56" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="J56" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K56" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L56" s="23"/>
+      <c r="M56" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N56" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N56" s="23"/>
+      <c r="O56" s="24" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <v>56</v>
       </c>
@@ -3309,8 +3470,8 @@
       <c r="H57" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="I57" s="6" t="s">
-        <v>16</v>
+      <c r="I57" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J57" s="5" t="s">
         <v>13</v>
@@ -3319,14 +3480,17 @@
         <v>13</v>
       </c>
       <c r="L57" s="5"/>
-      <c r="M57" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N57" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M57" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N57" s="5">
+        <v>4</v>
+      </c>
+      <c r="O57" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>57</v>
       </c>
@@ -3351,8 +3515,8 @@
       <c r="H58" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I58" s="6" t="s">
-        <v>16</v>
+      <c r="I58" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J58" s="5" t="s">
         <v>16</v>
@@ -3361,14 +3525,17 @@
         <v>13</v>
       </c>
       <c r="L58" s="5"/>
-      <c r="M58" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N58" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M58" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N58" s="5">
+        <v>2</v>
+      </c>
+      <c r="O58" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>58</v>
       </c>
@@ -3393,8 +3560,8 @@
       <c r="H59" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I59" s="6" t="s">
-        <v>16</v>
+      <c r="I59" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J59" s="5" t="s">
         <v>13</v>
@@ -3403,12 +3570,15 @@
         <v>13</v>
       </c>
       <c r="L59" s="5"/>
-      <c r="M59" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N59" s="6"/>
-    </row>
-    <row r="60" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M59" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N59" s="5">
+        <v>1</v>
+      </c>
+      <c r="O59" s="6"/>
+    </row>
+    <row r="60" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>59</v>
       </c>
@@ -3433,8 +3603,8 @@
       <c r="H60" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I60" s="6" t="s">
-        <v>16</v>
+      <c r="I60" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J60" s="5" t="s">
         <v>13</v>
@@ -3443,12 +3613,15 @@
         <v>13</v>
       </c>
       <c r="L60" s="5"/>
-      <c r="M60" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N60" s="6"/>
-    </row>
-    <row r="61" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M60" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N60" s="5">
+        <v>1</v>
+      </c>
+      <c r="O60" s="6"/>
+    </row>
+    <row r="61" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>60</v>
       </c>
@@ -3473,8 +3646,8 @@
       <c r="H61" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I61" s="6" t="s">
-        <v>16</v>
+      <c r="I61" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J61" s="5" t="s">
         <v>13</v>
@@ -3483,12 +3656,15 @@
         <v>13</v>
       </c>
       <c r="L61" s="5"/>
-      <c r="M61" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N61" s="6"/>
-    </row>
-    <row r="62" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M61" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N61" s="5">
+        <v>1</v>
+      </c>
+      <c r="O61" s="6"/>
+    </row>
+    <row r="62" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -3513,8 +3689,8 @@
       <c r="H62" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I62" s="6" t="s">
-        <v>16</v>
+      <c r="I62" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J62" s="5" t="s">
         <v>13</v>
@@ -3523,12 +3699,15 @@
         <v>13</v>
       </c>
       <c r="L62" s="5"/>
-      <c r="M62" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N62" s="6"/>
-    </row>
-    <row r="63" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M62" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N62" s="5">
+        <v>1</v>
+      </c>
+      <c r="O62" s="6"/>
+    </row>
+    <row r="63" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <v>62</v>
       </c>
@@ -3553,8 +3732,8 @@
       <c r="H63" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I63" s="6" t="s">
-        <v>16</v>
+      <c r="I63" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J63" s="5" t="s">
         <v>37</v>
@@ -3563,18 +3742,21 @@
         <v>37</v>
       </c>
       <c r="L63" s="5"/>
-      <c r="M63" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N63" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M63" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N63" s="5">
+        <v>2</v>
+      </c>
+      <c r="O63" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>63</v>
       </c>
-      <c r="B64" s="19">
+      <c r="B64" s="29">
         <v>34809</v>
       </c>
       <c r="C64" s="8" t="s">
@@ -3583,36 +3765,37 @@
       <c r="D64" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E64" s="22" t="s">
+      <c r="E64" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="F64" s="5">
-        <v>3</v>
-      </c>
-      <c r="G64" s="16">
+      <c r="F64" s="23">
+        <v>3</v>
+      </c>
+      <c r="G64" s="31">
         <v>10</v>
       </c>
-      <c r="H64" s="6" t="s">
+      <c r="H64" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="I64" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="J64" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K64" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L64" s="5"/>
-      <c r="M64" s="5" t="s">
+      <c r="I64" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="J64" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K64" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L64" s="23"/>
+      <c r="M64" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N64" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N64" s="23"/>
+      <c r="O64" s="24" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>64</v>
       </c>
@@ -3632,13 +3815,13 @@
         <v>3</v>
       </c>
       <c r="G65" s="16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="I65" s="5" t="s">
-        <v>16</v>
+        <v>70</v>
+      </c>
+      <c r="I65" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J65" s="5" t="s">
         <v>13</v>
@@ -3647,14 +3830,17 @@
         <v>13</v>
       </c>
       <c r="L65" s="5"/>
-      <c r="M65" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N65" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M65" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N65" s="5">
+        <v>3</v>
+      </c>
+      <c r="O65" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>65</v>
       </c>
@@ -3679,8 +3865,8 @@
       <c r="H66" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I66" s="6" t="s">
-        <v>16</v>
+      <c r="I66" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J66" s="5" t="s">
         <v>13</v>
@@ -3689,14 +3875,17 @@
         <v>13</v>
       </c>
       <c r="L66" s="5"/>
-      <c r="M66" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N66" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M66" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N66" s="5">
+        <v>2</v>
+      </c>
+      <c r="O66" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>66</v>
       </c>
@@ -3721,8 +3910,8 @@
       <c r="H67" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I67" s="6" t="s">
-        <v>16</v>
+      <c r="I67" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J67" s="5" t="s">
         <v>13</v>
@@ -3731,12 +3920,15 @@
         <v>13</v>
       </c>
       <c r="L67" s="5"/>
-      <c r="M67" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N67" s="6"/>
-    </row>
-    <row r="68" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M67" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N67" s="5">
+        <v>1</v>
+      </c>
+      <c r="O67" s="6"/>
+    </row>
+    <row r="68" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>67</v>
       </c>
@@ -3756,13 +3948,13 @@
         <v>3</v>
       </c>
       <c r="G68" s="16" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="H68" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I68" s="6" t="s">
-        <v>16</v>
+      <c r="I68" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J68" s="5" t="s">
         <v>13</v>
@@ -3771,14 +3963,17 @@
         <v>13</v>
       </c>
       <c r="L68" s="5"/>
-      <c r="M68" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N68" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M68" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N68" s="5">
+        <v>1</v>
+      </c>
+      <c r="O68" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>68</v>
       </c>
@@ -3801,10 +3996,10 @@
         <v>11</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="I69" s="5" t="s">
-        <v>16</v>
+        <v>72</v>
+      </c>
+      <c r="I69" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J69" s="5" t="s">
         <v>37</v>
@@ -3813,14 +4008,17 @@
         <v>37</v>
       </c>
       <c r="L69" s="5"/>
-      <c r="M69" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N69" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M69" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N69" s="5">
+        <v>1</v>
+      </c>
+      <c r="O69" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>69</v>
       </c>
@@ -3840,13 +4038,13 @@
         <v>3</v>
       </c>
       <c r="G70" s="16" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="H70" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I70" s="5" t="s">
-        <v>16</v>
+      <c r="I70" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J70" s="5" t="s">
         <v>13</v>
@@ -3855,14 +4053,17 @@
         <v>13</v>
       </c>
       <c r="L70" s="5"/>
-      <c r="M70" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N70" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M70" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N70" s="5">
+        <v>3</v>
+      </c>
+      <c r="O70" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <v>70</v>
       </c>
@@ -3887,8 +4088,8 @@
       <c r="H71" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I71" s="5" t="s">
-        <v>16</v>
+      <c r="I71" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J71" s="5" t="s">
         <v>13</v>
@@ -3897,12 +4098,15 @@
         <v>13</v>
       </c>
       <c r="L71" s="5"/>
-      <c r="M71" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N71" s="6"/>
-    </row>
-    <row r="72" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M71" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N71" s="5">
+        <v>1</v>
+      </c>
+      <c r="O71" s="6"/>
+    </row>
+    <row r="72" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>71</v>
       </c>
@@ -3927,8 +4131,8 @@
       <c r="H72" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I72" s="5" t="s">
-        <v>16</v>
+      <c r="I72" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J72" s="5" t="s">
         <v>37</v>
@@ -3937,12 +4141,15 @@
         <v>37</v>
       </c>
       <c r="L72" s="5"/>
-      <c r="M72" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N72" s="6"/>
-    </row>
-    <row r="73" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M72" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N72" s="5">
+        <v>1</v>
+      </c>
+      <c r="O72" s="6"/>
+    </row>
+    <row r="73" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <v>72</v>
       </c>
@@ -3967,8 +4174,8 @@
       <c r="H73" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I73" s="5" t="s">
-        <v>16</v>
+      <c r="I73" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J73" s="5" t="s">
         <v>13</v>
@@ -3977,12 +4184,15 @@
         <v>13</v>
       </c>
       <c r="L73" s="5"/>
-      <c r="M73" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N73" s="6"/>
-    </row>
-    <row r="74" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M73" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N73" s="5">
+        <v>1</v>
+      </c>
+      <c r="O73" s="6"/>
+    </row>
+    <row r="74" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>73</v>
       </c>
@@ -4007,8 +4217,8 @@
       <c r="H74" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I74" s="5" t="s">
-        <v>16</v>
+      <c r="I74" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J74" s="5" t="s">
         <v>13</v>
@@ -4017,16 +4227,19 @@
         <v>13</v>
       </c>
       <c r="L74" s="5"/>
-      <c r="M74" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N74" s="6"/>
-    </row>
-    <row r="75" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M74" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N74" s="5">
+        <v>1</v>
+      </c>
+      <c r="O74" s="6"/>
+    </row>
+    <row r="75" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <v>74</v>
       </c>
-      <c r="B75" s="19">
+      <c r="B75" s="29">
         <v>35138</v>
       </c>
       <c r="C75" s="8" t="s">
@@ -4035,40 +4248,41 @@
       <c r="D75" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E75" s="22" t="s">
+      <c r="E75" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="F75" s="5">
-        <v>3</v>
-      </c>
-      <c r="G75" s="16">
+      <c r="F75" s="23">
+        <v>3</v>
+      </c>
+      <c r="G75" s="31">
         <v>7</v>
       </c>
-      <c r="H75" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="I75" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="J75" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K75" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L75" s="5"/>
-      <c r="M75" s="5" t="s">
+      <c r="H75" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="I75" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="J75" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K75" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L75" s="23"/>
+      <c r="M75" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N75" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N75" s="23"/>
+      <c r="O75" s="24" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>75</v>
       </c>
-      <c r="B76" s="19">
+      <c r="B76" s="29">
         <v>35177</v>
       </c>
       <c r="C76" s="8" t="s">
@@ -4077,40 +4291,41 @@
       <c r="D76" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E76" s="22" t="s">
+      <c r="E76" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="F76" s="5">
-        <v>3</v>
-      </c>
-      <c r="G76" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I76" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="J76" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K76" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L76" s="5"/>
-      <c r="M76" s="5" t="s">
+      <c r="F76" s="23">
+        <v>3</v>
+      </c>
+      <c r="G76" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="H76" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="I76" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="J76" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K76" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L76" s="23"/>
+      <c r="M76" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N76" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N76" s="23"/>
+      <c r="O76" s="24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <v>76</v>
       </c>
-      <c r="B77" s="19">
+      <c r="B77" s="29">
         <v>35181</v>
       </c>
       <c r="C77" s="8" t="s">
@@ -4119,40 +4334,41 @@
       <c r="D77" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E77" s="22" t="s">
+      <c r="E77" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="F77" s="5">
-        <v>3</v>
-      </c>
-      <c r="G77" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="H77" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I77" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="J77" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K77" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L77" s="5"/>
-      <c r="M77" s="5" t="s">
+      <c r="F77" s="23">
+        <v>3</v>
+      </c>
+      <c r="G77" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="H77" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="I77" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="J77" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K77" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L77" s="23"/>
+      <c r="M77" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N77" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N77" s="23"/>
+      <c r="O77" s="24" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <v>77</v>
       </c>
-      <c r="B78" s="19">
+      <c r="B78" s="29">
         <v>35189</v>
       </c>
       <c r="C78" s="8" t="s">
@@ -4161,36 +4377,37 @@
       <c r="D78" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E78" s="22" t="s">
+      <c r="E78" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="F78" s="5">
-        <v>3</v>
-      </c>
-      <c r="G78" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="H78" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="I78" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="J78" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="K78" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="L78" s="5"/>
-      <c r="M78" s="16" t="s">
+      <c r="F78" s="23">
+        <v>3</v>
+      </c>
+      <c r="G78" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="H78" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="I78" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="J78" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="K78" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="L78" s="23"/>
+      <c r="M78" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="N78" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N78" s="31"/>
+      <c r="O78" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <v>78</v>
       </c>
@@ -4215,8 +4432,8 @@
       <c r="H79" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I79" s="5" t="s">
-        <v>16</v>
+      <c r="I79" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J79" s="5" t="s">
         <v>16</v>
@@ -4225,14 +4442,17 @@
         <v>13</v>
       </c>
       <c r="L79" s="5"/>
-      <c r="M79" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N79" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M79" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N79" s="5">
+        <v>2</v>
+      </c>
+      <c r="O79" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <v>79</v>
       </c>
@@ -4257,8 +4477,8 @@
       <c r="H80" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I80" s="5" t="s">
-        <v>16</v>
+      <c r="I80" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J80" s="5" t="s">
         <v>13</v>
@@ -4267,16 +4487,19 @@
         <v>13</v>
       </c>
       <c r="L80" s="5"/>
-      <c r="M80" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N80" s="6"/>
-    </row>
-    <row r="81" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M80" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N80" s="5">
+        <v>1</v>
+      </c>
+      <c r="O80" s="6"/>
+    </row>
+    <row r="81" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <v>80</v>
       </c>
-      <c r="B81" s="19">
+      <c r="B81" s="29">
         <v>72981</v>
       </c>
       <c r="C81" s="8" t="s">
@@ -4285,36 +4508,37 @@
       <c r="D81" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E81" s="22" t="s">
+      <c r="E81" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="F81" s="5">
-        <v>3</v>
-      </c>
-      <c r="G81" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H81" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="I81" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J81" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K81" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L81" s="5"/>
-      <c r="M81" s="5" t="s">
+      <c r="F81" s="23">
+        <v>3</v>
+      </c>
+      <c r="G81" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="H81" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="I81" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J81" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K81" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L81" s="23"/>
+      <c r="M81" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N81" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N81" s="23"/>
+      <c r="O81" s="24" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <v>81</v>
       </c>
@@ -4339,8 +4563,8 @@
       <c r="H82" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I82" s="5" t="s">
-        <v>16</v>
+      <c r="I82" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J82" s="5" t="s">
         <v>13</v>
@@ -4349,12 +4573,15 @@
         <v>13</v>
       </c>
       <c r="L82" s="5"/>
-      <c r="M82" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N82" s="5"/>
-    </row>
-    <row r="83" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M82" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N82" s="5">
+        <v>1</v>
+      </c>
+      <c r="O82" s="5"/>
+    </row>
+    <row r="83" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <v>82</v>
       </c>
@@ -4379,8 +4606,8 @@
       <c r="H83" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I83" s="5" t="s">
-        <v>16</v>
+      <c r="I83" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J83" s="5" t="s">
         <v>13</v>
@@ -4389,14 +4616,17 @@
         <v>13</v>
       </c>
       <c r="L83" s="5"/>
-      <c r="M83" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N83" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M83" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N83" s="5">
+        <v>5</v>
+      </c>
+      <c r="O83" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
         <v>83</v>
       </c>
@@ -4421,8 +4651,8 @@
       <c r="H84" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I84" s="5" t="s">
-        <v>16</v>
+      <c r="I84" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J84" s="5" t="s">
         <v>16</v>
@@ -4431,14 +4661,17 @@
         <v>37</v>
       </c>
       <c r="L84" s="5"/>
-      <c r="M84" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N84" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M84" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N84" s="5">
+        <v>2</v>
+      </c>
+      <c r="O84" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <v>84</v>
       </c>
@@ -4458,13 +4691,13 @@
         <v>3</v>
       </c>
       <c r="G85" s="16" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H85" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I85" s="5" t="s">
-        <v>16</v>
+      <c r="I85" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J85" s="5" t="s">
         <v>13</v>
@@ -4473,14 +4706,17 @@
         <v>13</v>
       </c>
       <c r="L85" s="5"/>
-      <c r="M85" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N85" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M85" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N85" s="5">
+        <v>2</v>
+      </c>
+      <c r="O85" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <v>85</v>
       </c>
@@ -4505,8 +4741,8 @@
       <c r="H86" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I86" s="5" t="s">
-        <v>16</v>
+      <c r="I86" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J86" s="5" t="s">
         <v>16</v>
@@ -4515,14 +4751,17 @@
         <v>37</v>
       </c>
       <c r="L86" s="5"/>
-      <c r="M86" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N86" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M86" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N86" s="5">
+        <v>2</v>
+      </c>
+      <c r="O86" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
         <v>86</v>
       </c>
@@ -4547,8 +4786,8 @@
       <c r="H87" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I87" s="5" t="s">
-        <v>16</v>
+      <c r="I87" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J87" s="5" t="s">
         <v>16</v>
@@ -4557,14 +4796,17 @@
         <v>37</v>
       </c>
       <c r="L87" s="5"/>
-      <c r="M87" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N87" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M87" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N87" s="5">
+        <v>3</v>
+      </c>
+      <c r="O87" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
         <v>87</v>
       </c>
@@ -4589,8 +4831,8 @@
       <c r="H88" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I88" s="5" t="s">
-        <v>16</v>
+      <c r="I88" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J88" s="5" t="s">
         <v>16</v>
@@ -4599,14 +4841,17 @@
         <v>37</v>
       </c>
       <c r="L88" s="5"/>
-      <c r="M88" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N88" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M88" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N88" s="5">
+        <v>3</v>
+      </c>
+      <c r="O88" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
         <v>88</v>
       </c>
@@ -4631,8 +4876,8 @@
       <c r="H89" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I89" s="5" t="s">
-        <v>16</v>
+      <c r="I89" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J89" s="5" t="s">
         <v>16</v>
@@ -4641,18 +4886,21 @@
         <v>37</v>
       </c>
       <c r="L89" s="5"/>
-      <c r="M89" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N89" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M89" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N89" s="5">
+        <v>1</v>
+      </c>
+      <c r="O89" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <v>89</v>
       </c>
-      <c r="B90" s="19">
+      <c r="B90" s="29">
         <v>142503</v>
       </c>
       <c r="C90" s="8" t="s">
@@ -4661,40 +4909,41 @@
       <c r="D90" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E90" s="22" t="s">
+      <c r="E90" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="F90" s="5">
-        <v>3</v>
-      </c>
-      <c r="G90" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="H90" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="I90" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="J90" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K90" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L90" s="5"/>
-      <c r="M90" s="5" t="s">
+      <c r="F90" s="23">
+        <v>3</v>
+      </c>
+      <c r="G90" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="H90" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="I90" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="J90" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K90" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L90" s="23"/>
+      <c r="M90" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N90" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N90" s="23"/>
+      <c r="O90" s="23" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
         <v>90</v>
       </c>
-      <c r="B91" s="19">
+      <c r="B91" s="29">
         <v>142512</v>
       </c>
       <c r="C91" s="8" t="s">
@@ -4703,40 +4952,41 @@
       <c r="D91" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E91" s="22" t="s">
+      <c r="E91" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="F91" s="5">
-        <v>3</v>
-      </c>
-      <c r="G91" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="H91" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="I91" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="J91" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K91" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L91" s="5"/>
-      <c r="M91" s="5" t="s">
+      <c r="F91" s="23">
+        <v>3</v>
+      </c>
+      <c r="G91" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="H91" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="I91" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="J91" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K91" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L91" s="23"/>
+      <c r="M91" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N91" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N91" s="23"/>
+      <c r="O91" s="23" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
         <v>91</v>
       </c>
-      <c r="B92" s="19">
+      <c r="B92" s="29">
         <v>143477</v>
       </c>
       <c r="C92" s="8" t="s">
@@ -4745,40 +4995,41 @@
       <c r="D92" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E92" s="22" t="s">
+      <c r="E92" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="F92" s="5">
-        <v>3</v>
-      </c>
-      <c r="G92" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="H92" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="I92" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="J92" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K92" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L92" s="5"/>
-      <c r="M92" s="5" t="s">
+      <c r="F92" s="23">
+        <v>3</v>
+      </c>
+      <c r="G92" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="H92" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="I92" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="J92" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K92" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L92" s="23"/>
+      <c r="M92" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N92" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N92" s="23"/>
+      <c r="O92" s="24" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
         <v>92</v>
       </c>
-      <c r="B93" s="19">
+      <c r="B93" s="29">
         <v>191750</v>
       </c>
       <c r="C93" s="8" t="s">
@@ -4787,40 +5038,41 @@
       <c r="D93" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E93" s="22" t="s">
+      <c r="E93" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F93" s="5">
-        <v>3</v>
-      </c>
-      <c r="G93" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H93" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I93" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="J93" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="K93" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="L93" s="5"/>
-      <c r="M93" s="5" t="s">
+      <c r="F93" s="23">
+        <v>3</v>
+      </c>
+      <c r="G93" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="H93" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="I93" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="J93" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="K93" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="L93" s="23"/>
+      <c r="M93" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N93" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N93" s="23"/>
+      <c r="O93" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
         <v>93</v>
       </c>
-      <c r="B94" s="19">
+      <c r="B94" s="29">
         <v>191753</v>
       </c>
       <c r="C94" s="8" t="s">
@@ -4829,40 +5081,41 @@
       <c r="D94" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E94" s="22" t="s">
+      <c r="E94" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F94" s="5">
-        <v>3</v>
-      </c>
-      <c r="G94" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H94" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I94" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="J94" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="K94" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="L94" s="5"/>
-      <c r="M94" s="5" t="s">
+      <c r="F94" s="23">
+        <v>3</v>
+      </c>
+      <c r="G94" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="H94" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="I94" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="J94" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="K94" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="L94" s="23"/>
+      <c r="M94" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N94" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N94" s="23"/>
+      <c r="O94" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
         <v>94</v>
       </c>
-      <c r="B95" s="19">
+      <c r="B95" s="29">
         <v>191810</v>
       </c>
       <c r="C95" s="8" t="s">
@@ -4871,40 +5124,41 @@
       <c r="D95" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E95" s="22" t="s">
+      <c r="E95" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F95" s="5">
-        <v>3</v>
-      </c>
-      <c r="G95" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H95" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I95" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="J95" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="K95" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="L95" s="5"/>
-      <c r="M95" s="5" t="s">
+      <c r="F95" s="23">
+        <v>3</v>
+      </c>
+      <c r="G95" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="H95" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="I95" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="J95" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="K95" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="L95" s="23"/>
+      <c r="M95" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N95" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N95" s="23"/>
+      <c r="O95" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
         <v>95</v>
       </c>
-      <c r="B96" s="19">
+      <c r="B96" s="29">
         <v>191811</v>
       </c>
       <c r="C96" s="8" t="s">
@@ -4913,40 +5167,41 @@
       <c r="D96" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E96" s="22" t="s">
+      <c r="E96" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F96" s="5">
-        <v>3</v>
-      </c>
-      <c r="G96" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H96" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I96" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="J96" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="K96" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="L96" s="5"/>
-      <c r="M96" s="5" t="s">
+      <c r="F96" s="23">
+        <v>3</v>
+      </c>
+      <c r="G96" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="H96" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="I96" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="J96" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="K96" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="L96" s="23"/>
+      <c r="M96" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N96" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N96" s="23"/>
+      <c r="O96" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
         <v>96</v>
       </c>
-      <c r="B97" s="19">
+      <c r="B97" s="29">
         <v>191815</v>
       </c>
       <c r="C97" s="8" t="s">
@@ -4955,40 +5210,41 @@
       <c r="D97" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E97" s="22" t="s">
+      <c r="E97" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F97" s="5">
-        <v>3</v>
-      </c>
-      <c r="G97" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H97" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I97" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="J97" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="K97" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="L97" s="5"/>
-      <c r="M97" s="5" t="s">
+      <c r="F97" s="23">
+        <v>3</v>
+      </c>
+      <c r="G97" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="H97" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="I97" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="J97" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="K97" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="L97" s="23"/>
+      <c r="M97" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N97" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N97" s="23"/>
+      <c r="O97" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
         <v>97</v>
       </c>
-      <c r="B98" s="19">
+      <c r="B98" s="29">
         <v>191819</v>
       </c>
       <c r="C98" s="8" t="s">
@@ -4997,40 +5253,41 @@
       <c r="D98" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E98" s="22" t="s">
+      <c r="E98" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F98" s="5">
-        <v>3</v>
-      </c>
-      <c r="G98" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H98" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I98" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="J98" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="K98" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="L98" s="5"/>
-      <c r="M98" s="5" t="s">
+      <c r="F98" s="23">
+        <v>3</v>
+      </c>
+      <c r="G98" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="H98" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="I98" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="J98" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="K98" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="L98" s="23"/>
+      <c r="M98" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N98" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N98" s="23"/>
+      <c r="O98" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <v>98</v>
       </c>
-      <c r="B99" s="19">
+      <c r="B99" s="29">
         <v>191825</v>
       </c>
       <c r="C99" s="8" t="s">
@@ -5039,40 +5296,41 @@
       <c r="D99" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E99" s="22" t="s">
+      <c r="E99" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F99" s="5">
-        <v>3</v>
-      </c>
-      <c r="G99" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H99" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I99" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="J99" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="K99" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="L99" s="5"/>
-      <c r="M99" s="5" t="s">
+      <c r="F99" s="23">
+        <v>3</v>
+      </c>
+      <c r="G99" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="H99" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="I99" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="J99" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="K99" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="L99" s="23"/>
+      <c r="M99" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N99" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N99" s="23"/>
+      <c r="O99" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
         <v>99</v>
       </c>
-      <c r="B100" s="19">
+      <c r="B100" s="29">
         <v>191830</v>
       </c>
       <c r="C100" s="8" t="s">
@@ -5081,40 +5339,41 @@
       <c r="D100" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E100" s="22" t="s">
+      <c r="E100" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F100" s="5">
-        <v>3</v>
-      </c>
-      <c r="G100" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H100" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I100" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="J100" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="K100" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="L100" s="5"/>
-      <c r="M100" s="5" t="s">
+      <c r="F100" s="23">
+        <v>3</v>
+      </c>
+      <c r="G100" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="H100" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="I100" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="J100" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="K100" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="L100" s="23"/>
+      <c r="M100" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N100" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N100" s="23"/>
+      <c r="O100" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>100</v>
       </c>
-      <c r="B101" s="19">
+      <c r="B101" s="29">
         <v>191832</v>
       </c>
       <c r="C101" s="8" t="s">
@@ -5123,40 +5382,41 @@
       <c r="D101" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E101" s="22" t="s">
+      <c r="E101" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F101" s="5">
-        <v>3</v>
-      </c>
-      <c r="G101" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H101" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I101" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="J101" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="K101" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="L101" s="5"/>
-      <c r="M101" s="5" t="s">
+      <c r="F101" s="23">
+        <v>3</v>
+      </c>
+      <c r="G101" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="H101" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="I101" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="J101" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="K101" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="L101" s="23"/>
+      <c r="M101" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N101" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N101" s="23"/>
+      <c r="O101" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
         <v>101</v>
       </c>
-      <c r="B102" s="19">
+      <c r="B102" s="29">
         <v>191840</v>
       </c>
       <c r="C102" s="8" t="s">
@@ -5165,40 +5425,41 @@
       <c r="D102" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E102" s="22" t="s">
+      <c r="E102" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F102" s="5">
-        <v>3</v>
-      </c>
-      <c r="G102" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H102" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I102" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="J102" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="K102" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="L102" s="5"/>
-      <c r="M102" s="5" t="s">
+      <c r="F102" s="23">
+        <v>3</v>
+      </c>
+      <c r="G102" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="H102" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="I102" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="J102" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="K102" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="L102" s="23"/>
+      <c r="M102" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N102" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N102" s="23"/>
+      <c r="O102" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
         <v>102</v>
       </c>
-      <c r="B103" s="19">
+      <c r="B103" s="29">
         <v>191841</v>
       </c>
       <c r="C103" s="8" t="s">
@@ -5207,40 +5468,41 @@
       <c r="D103" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E103" s="22" t="s">
+      <c r="E103" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F103" s="5">
-        <v>3</v>
-      </c>
-      <c r="G103" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H103" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I103" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="J103" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="K103" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="L103" s="5"/>
-      <c r="M103" s="5" t="s">
+      <c r="F103" s="23">
+        <v>3</v>
+      </c>
+      <c r="G103" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="H103" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="I103" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="J103" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="K103" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="L103" s="23"/>
+      <c r="M103" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N103" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N103" s="23"/>
+      <c r="O103" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
         <v>103</v>
       </c>
-      <c r="B104" s="19">
+      <c r="B104" s="29">
         <v>191847</v>
       </c>
       <c r="C104" s="8" t="s">
@@ -5249,40 +5511,41 @@
       <c r="D104" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E104" s="22" t="s">
+      <c r="E104" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F104" s="5">
-        <v>3</v>
-      </c>
-      <c r="G104" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H104" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I104" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="J104" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="K104" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="L104" s="5"/>
-      <c r="M104" s="5" t="s">
+      <c r="F104" s="23">
+        <v>3</v>
+      </c>
+      <c r="G104" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="H104" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="I104" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="J104" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="K104" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="L104" s="23"/>
+      <c r="M104" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N104" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="105" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N104" s="23"/>
+      <c r="O104" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
         <v>104</v>
       </c>
-      <c r="B105" s="19">
+      <c r="B105" s="29">
         <v>191850</v>
       </c>
       <c r="C105" s="8" t="s">
@@ -5291,40 +5554,41 @@
       <c r="D105" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E105" s="22" t="s">
+      <c r="E105" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F105" s="5">
-        <v>3</v>
-      </c>
-      <c r="G105" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H105" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I105" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="J105" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="K105" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="L105" s="5"/>
-      <c r="M105" s="5" t="s">
+      <c r="F105" s="23">
+        <v>3</v>
+      </c>
+      <c r="G105" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="H105" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="I105" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="J105" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="K105" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="L105" s="23"/>
+      <c r="M105" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N105" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="106" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N105" s="23"/>
+      <c r="O105" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
         <v>105</v>
       </c>
-      <c r="B106" s="19">
+      <c r="B106" s="29">
         <v>191855</v>
       </c>
       <c r="C106" s="8" t="s">
@@ -5333,40 +5597,41 @@
       <c r="D106" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E106" s="22" t="s">
+      <c r="E106" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F106" s="5">
-        <v>3</v>
-      </c>
-      <c r="G106" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H106" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I106" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="J106" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="K106" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="L106" s="5"/>
-      <c r="M106" s="5" t="s">
+      <c r="F106" s="23">
+        <v>3</v>
+      </c>
+      <c r="G106" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="H106" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="I106" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="J106" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="K106" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="L106" s="23"/>
+      <c r="M106" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N106" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="107" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N106" s="23"/>
+      <c r="O106" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
         <v>106</v>
       </c>
-      <c r="B107" s="19">
+      <c r="B107" s="29">
         <v>191861</v>
       </c>
       <c r="C107" s="8" t="s">
@@ -5375,40 +5640,41 @@
       <c r="D107" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E107" s="22" t="s">
+      <c r="E107" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F107" s="5">
-        <v>3</v>
-      </c>
-      <c r="G107" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H107" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I107" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="J107" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="K107" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="L107" s="5"/>
-      <c r="M107" s="5" t="s">
+      <c r="F107" s="23">
+        <v>3</v>
+      </c>
+      <c r="G107" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="H107" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="I107" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="J107" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="K107" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="L107" s="23"/>
+      <c r="M107" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N107" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="108" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N107" s="23"/>
+      <c r="O107" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
         <v>107</v>
       </c>
-      <c r="B108" s="19">
+      <c r="B108" s="29">
         <v>191869</v>
       </c>
       <c r="C108" s="8" t="s">
@@ -5417,40 +5683,41 @@
       <c r="D108" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E108" s="22" t="s">
+      <c r="E108" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F108" s="5">
-        <v>3</v>
-      </c>
-      <c r="G108" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H108" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I108" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="J108" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="K108" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="L108" s="5"/>
-      <c r="M108" s="5" t="s">
+      <c r="F108" s="23">
+        <v>3</v>
+      </c>
+      <c r="G108" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="H108" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="I108" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="J108" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="K108" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="L108" s="23"/>
+      <c r="M108" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N108" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="109" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N108" s="23"/>
+      <c r="O108" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="5">
         <v>108</v>
       </c>
-      <c r="B109" s="19">
+      <c r="B109" s="29">
         <v>191871</v>
       </c>
       <c r="C109" s="8" t="s">
@@ -5459,40 +5726,41 @@
       <c r="D109" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E109" s="22" t="s">
+      <c r="E109" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F109" s="5">
-        <v>3</v>
-      </c>
-      <c r="G109" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H109" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I109" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="J109" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="K109" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="L109" s="5"/>
-      <c r="M109" s="5" t="s">
+      <c r="F109" s="23">
+        <v>3</v>
+      </c>
+      <c r="G109" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="H109" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="I109" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="J109" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="K109" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="L109" s="23"/>
+      <c r="M109" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N109" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="110" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N109" s="23"/>
+      <c r="O109" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
         <v>109</v>
       </c>
-      <c r="B110" s="19">
+      <c r="B110" s="29">
         <v>191875</v>
       </c>
       <c r="C110" s="8" t="s">
@@ -5501,40 +5769,41 @@
       <c r="D110" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E110" s="22" t="s">
+      <c r="E110" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F110" s="5">
-        <v>3</v>
-      </c>
-      <c r="G110" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H110" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I110" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="J110" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="K110" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="L110" s="5"/>
-      <c r="M110" s="5" t="s">
+      <c r="F110" s="23">
+        <v>3</v>
+      </c>
+      <c r="G110" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="H110" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="I110" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="J110" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="K110" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="L110" s="23"/>
+      <c r="M110" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N110" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="111" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N110" s="23"/>
+      <c r="O110" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
         <v>110</v>
       </c>
-      <c r="B111" s="19">
+      <c r="B111" s="29">
         <v>30883</v>
       </c>
       <c r="C111" s="8" t="s">
@@ -5543,26 +5812,27 @@
       <c r="D111" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E111" s="22" t="s">
+      <c r="E111" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="F111" s="5">
-        <v>3</v>
-      </c>
-      <c r="G111" s="16"/>
-      <c r="H111" s="5"/>
-      <c r="I111" s="6"/>
-      <c r="J111" s="5"/>
-      <c r="K111" s="5"/>
-      <c r="L111" s="5"/>
-      <c r="M111" s="5" t="s">
+      <c r="F111" s="23">
+        <v>3</v>
+      </c>
+      <c r="G111" s="31"/>
+      <c r="H111" s="23"/>
+      <c r="I111" s="24"/>
+      <c r="J111" s="23"/>
+      <c r="K111" s="23"/>
+      <c r="L111" s="23"/>
+      <c r="M111" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N111" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="112" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N111" s="23"/>
+      <c r="O111" s="23" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
         <v>111</v>
       </c>
@@ -5585,10 +5855,10 @@
         <v>2</v>
       </c>
       <c r="H112" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="I112" s="6" t="s">
-        <v>16</v>
+        <v>98</v>
+      </c>
+      <c r="I112" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J112" s="5" t="s">
         <v>16</v>
@@ -5597,12 +5867,15 @@
         <v>13</v>
       </c>
       <c r="L112" s="5"/>
-      <c r="M112" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N112" s="5"/>
-    </row>
-    <row r="113" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M112" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N112" s="5">
+        <v>1</v>
+      </c>
+      <c r="O112" s="5"/>
+    </row>
+    <row r="113" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
         <v>112</v>
       </c>
@@ -5625,10 +5898,10 @@
         <v>2</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="I113" s="6" t="s">
-        <v>16</v>
+        <v>98</v>
+      </c>
+      <c r="I113" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J113" s="5" t="s">
         <v>16</v>
@@ -5637,12 +5910,15 @@
         <v>13</v>
       </c>
       <c r="L113" s="5"/>
-      <c r="M113" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N113" s="5"/>
-    </row>
-    <row r="114" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M113" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N113" s="5">
+        <v>1</v>
+      </c>
+      <c r="O113" s="5"/>
+    </row>
+    <row r="114" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
         <v>113</v>
       </c>
@@ -5665,10 +5941,10 @@
         <v>2</v>
       </c>
       <c r="H114" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="I114" s="6" t="s">
-        <v>16</v>
+        <v>98</v>
+      </c>
+      <c r="I114" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J114" s="5" t="s">
         <v>16</v>
@@ -5677,14 +5953,17 @@
         <v>13</v>
       </c>
       <c r="L114" s="5"/>
-      <c r="M114" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N114" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="115" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M114" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N114" s="5">
+        <v>1</v>
+      </c>
+      <c r="O114" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
         <v>114</v>
       </c>
@@ -5707,10 +5986,10 @@
         <v>2</v>
       </c>
       <c r="H115" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="I115" s="6" t="s">
-        <v>16</v>
+        <v>98</v>
+      </c>
+      <c r="I115" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J115" s="5" t="s">
         <v>16</v>
@@ -5719,14 +5998,17 @@
         <v>13</v>
       </c>
       <c r="L115" s="5"/>
-      <c r="M115" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N115" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="116" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M115" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N115" s="5">
+        <v>1</v>
+      </c>
+      <c r="O115" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
         <v>115</v>
       </c>
@@ -5749,10 +6031,10 @@
         <v>2</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="I116" s="6" t="s">
-        <v>16</v>
+        <v>98</v>
+      </c>
+      <c r="I116" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="J116" s="5" t="s">
         <v>16</v>
@@ -5761,16 +6043,19 @@
         <v>37</v>
       </c>
       <c r="L116" s="5"/>
-      <c r="M116" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N116" s="5"/>
-    </row>
-    <row r="117" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M116" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N116" s="5">
+        <v>1</v>
+      </c>
+      <c r="O116" s="5"/>
+    </row>
+    <row r="117" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
         <v>116</v>
       </c>
-      <c r="B117" s="19">
+      <c r="B117" s="29">
         <v>142452</v>
       </c>
       <c r="C117" s="8" t="s">
@@ -5779,36 +6064,37 @@
       <c r="D117" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E117" s="22" t="s">
+      <c r="E117" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="F117" s="5">
-        <v>3</v>
-      </c>
-      <c r="G117" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H117" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="I117" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="J117" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="K117" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L117" s="5"/>
-      <c r="M117" s="5" t="s">
+      <c r="F117" s="23">
+        <v>3</v>
+      </c>
+      <c r="G117" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="H117" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="I117" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="J117" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="K117" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L117" s="23"/>
+      <c r="M117" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N117" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="118" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N117" s="23"/>
+      <c r="O117" s="23" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
         <v>117</v>
       </c>
@@ -5831,10 +6117,10 @@
         <v>4</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="I118" s="6" t="s">
-        <v>16</v>
+        <v>102</v>
+      </c>
+      <c r="I118" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J118" s="5" t="s">
         <v>13</v>
@@ -5843,18 +6129,21 @@
         <v>13</v>
       </c>
       <c r="L118" s="5"/>
-      <c r="M118" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N118" s="5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="119" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M118" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N118" s="5">
+        <v>2</v>
+      </c>
+      <c r="O118" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="5">
         <v>118</v>
       </c>
-      <c r="B119" s="19">
+      <c r="B119" s="29">
         <v>30937</v>
       </c>
       <c r="C119" s="8" t="s">
@@ -5863,40 +6152,41 @@
       <c r="D119" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E119" s="22" t="s">
+      <c r="E119" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="F119" s="5">
-        <v>3</v>
-      </c>
-      <c r="G119" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H119" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I119" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="J119" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="K119" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="L119" s="5"/>
-      <c r="M119" s="5" t="s">
+      <c r="F119" s="23">
+        <v>3</v>
+      </c>
+      <c r="G119" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="H119" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="I119" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="J119" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="K119" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="L119" s="23"/>
+      <c r="M119" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N119" s="30" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="120" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N119" s="23"/>
+      <c r="O119" s="34" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
         <v>119</v>
       </c>
-      <c r="B120" s="19">
+      <c r="B120" s="29">
         <v>30940</v>
       </c>
       <c r="C120" s="8" t="s">
@@ -5905,40 +6195,41 @@
       <c r="D120" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E120" s="22" t="s">
+      <c r="E120" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="F120" s="5">
-        <v>3</v>
-      </c>
-      <c r="G120" s="16">
+      <c r="F120" s="23">
+        <v>3</v>
+      </c>
+      <c r="G120" s="31">
         <v>9</v>
       </c>
-      <c r="H120" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="I120" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="J120" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K120" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L120" s="5"/>
-      <c r="M120" s="5" t="s">
+      <c r="H120" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="I120" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="J120" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K120" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L120" s="23"/>
+      <c r="M120" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N120" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="121" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N120" s="23"/>
+      <c r="O120" s="23" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
         <v>120</v>
       </c>
-      <c r="B121" s="19">
+      <c r="B121" s="29">
         <v>30982</v>
       </c>
       <c r="C121" s="8" t="s">
@@ -5947,36 +6238,37 @@
       <c r="D121" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E121" s="22" t="s">
+      <c r="E121" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="F121" s="5">
-        <v>3</v>
-      </c>
-      <c r="G121" s="16">
+      <c r="F121" s="23">
+        <v>3</v>
+      </c>
+      <c r="G121" s="31">
         <v>8</v>
       </c>
-      <c r="H121" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I121" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="J121" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K121" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L121" s="5"/>
-      <c r="M121" s="5" t="s">
+      <c r="H121" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="I121" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="J121" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K121" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L121" s="23"/>
+      <c r="M121" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N121" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="122" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N121" s="23"/>
+      <c r="O121" s="23" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="5">
         <v>121</v>
       </c>
@@ -5999,10 +6291,10 @@
         <v>3</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="I122" s="6" t="s">
-        <v>16</v>
+        <v>104</v>
+      </c>
+      <c r="I122" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J122" s="5" t="s">
         <v>13</v>
@@ -6011,18 +6303,21 @@
         <v>13</v>
       </c>
       <c r="L122" s="5"/>
-      <c r="M122" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N122" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="123" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M122" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N122" s="5">
+        <v>1</v>
+      </c>
+      <c r="O122" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
         <v>122</v>
       </c>
-      <c r="B123" s="19">
+      <c r="B123" s="29">
         <v>191698</v>
       </c>
       <c r="C123" s="8" t="s">
@@ -6031,40 +6326,41 @@
       <c r="D123" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E123" s="22" t="s">
+      <c r="E123" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="F123" s="5">
-        <v>3</v>
-      </c>
-      <c r="G123" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="H123" s="8" t="s">
+      <c r="F123" s="23">
+        <v>3</v>
+      </c>
+      <c r="G123" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="H123" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="I123" s="8" t="s">
+      <c r="I123" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="J123" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K123" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L123" s="8"/>
-      <c r="M123" s="8" t="s">
+      <c r="J123" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K123" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L123" s="23"/>
+      <c r="M123" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N123" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="124" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N123" s="23"/>
+      <c r="O123" s="24" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="5">
         <v>123</v>
       </c>
-      <c r="B124" s="19">
+      <c r="B124" s="29">
         <v>191699</v>
       </c>
       <c r="C124" s="8" t="s">
@@ -6073,40 +6369,41 @@
       <c r="D124" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E124" s="22" t="s">
+      <c r="E124" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="F124" s="5">
-        <v>3</v>
-      </c>
-      <c r="G124" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="H124" s="8" t="s">
+      <c r="F124" s="23">
+        <v>3</v>
+      </c>
+      <c r="G124" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="H124" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="I124" s="8" t="s">
+      <c r="I124" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="J124" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K124" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L124" s="8"/>
-      <c r="M124" s="8" t="s">
+      <c r="J124" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K124" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L124" s="23"/>
+      <c r="M124" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N124" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="125" spans="1:14" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N124" s="23"/>
+      <c r="O124" s="23" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
         <v>124</v>
       </c>
-      <c r="B125" s="19">
+      <c r="B125" s="29">
         <v>191700</v>
       </c>
       <c r="C125" s="8" t="s">
@@ -6115,36 +6412,37 @@
       <c r="D125" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E125" s="22" t="s">
+      <c r="E125" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="F125" s="5">
-        <v>3</v>
-      </c>
-      <c r="G125" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="H125" s="8" t="s">
+      <c r="F125" s="23">
+        <v>3</v>
+      </c>
+      <c r="G125" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="H125" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="I125" s="8" t="s">
+      <c r="I125" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="J125" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K125" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L125" s="8"/>
-      <c r="M125" s="8" t="s">
+      <c r="J125" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K125" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L125" s="23"/>
+      <c r="M125" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N125" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="126" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N125" s="23"/>
+      <c r="O125" s="23" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="5">
         <v>125</v>
       </c>
@@ -6164,13 +6462,13 @@
         <v>3</v>
       </c>
       <c r="G126" s="16" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="H126" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I126" s="6" t="s">
-        <v>16</v>
+      <c r="I126" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J126" s="6" t="s">
         <v>13</v>
@@ -6179,12 +6477,15 @@
         <v>13</v>
       </c>
       <c r="L126" s="5"/>
-      <c r="M126" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N126" s="6"/>
-    </row>
-    <row r="127" spans="1:14" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M126" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N126" s="5">
+        <v>1</v>
+      </c>
+      <c r="O126" s="6"/>
+    </row>
+    <row r="127" spans="1:15" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
         <v>126</v>
       </c>
@@ -6204,13 +6505,13 @@
         <v>3</v>
       </c>
       <c r="G127" s="16" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="H127" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I127" s="6" t="s">
-        <v>16</v>
+      <c r="I127" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="J127" s="6" t="s">
         <v>13</v>
@@ -6219,12 +6520,15 @@
         <v>13</v>
       </c>
       <c r="L127" s="5"/>
-      <c r="M127" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N127" s="6"/>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M127" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="N127" s="5">
+        <v>1</v>
+      </c>
+      <c r="O127" s="6"/>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" s="10"/>
       <c r="B128" s="20"/>
       <c r="C128" s="10"/>
@@ -6238,9 +6542,19 @@
       <c r="K128" s="11"/>
       <c r="L128" s="11"/>
       <c r="M128" s="10"/>
+      <c r="N128" s="10"/>
+    </row>
+    <row r="129" spans="13:14" x14ac:dyDescent="0.25">
+      <c r="M129" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="N129" s="7">
+        <f>SUBTOTAL(9,N2:N128)</f>
+        <v>88</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P127">
+  <autoFilter ref="A1:Q127">
     <filterColumn colId="12">
       <filters>
         <filter val="EVET"/>
